--- a/data/trans_camb/P5B_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P5B_R-Clase-trans_camb.xlsx
@@ -624,7 +624,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0,85</t>
+          <t>0,89</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -639,7 +639,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,05</t>
+          <t>-0,03</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -649,12 +649,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-0,73</t>
+          <t>-0,72</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,24</t>
+          <t>0,26</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-2,09</t>
+          <t>-2,08</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 6,58</t>
+          <t>-4,04; 6,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,23; -0,99</t>
+          <t>-8,73; -0,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,58; -0,97</t>
+          <t>-9,1; -0,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 3,54</t>
+          <t>-3,64; 2,85</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,6; 0,0</t>
+          <t>-6,02; 0,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 1,89</t>
+          <t>-4,56; 1,57</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 3,54</t>
+          <t>-2,75; 3,57</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,4; -0,95</t>
+          <t>-5,96; -1,24</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-5,49; -0,12</t>
+          <t>-5,17; -0,12</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-2,69%</t>
+          <t>-1,69%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -755,12 +755,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-40,15%</t>
+          <t>-39,42%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-77,23%</t>
+          <t>-77,0%</t>
         </is>
       </c>
     </row>
@@ -783,7 +783,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-80,98; 585,94</t>
+          <t>-100,0; 627,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-71,24; 328,7</t>
+          <t>-72,94; 322,6</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 70,58</t>
+          <t>-100,0; 106,96</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-2,23</t>
+          <t>-2,21</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>-1,38</t>
+          <t>-1,37</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 4,95</t>
+          <t>-4,93; 5,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,26; 0,51</t>
+          <t>-7,26; 0,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,19; 0,33</t>
+          <t>-7,07; 0,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 1,99</t>
+          <t>-7,2; 1,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-8,1; 0,1</t>
+          <t>-7,81; 0,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 3,31</t>
+          <t>-5,65; 3,63</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 1,84</t>
+          <t>-4,38; 1,81</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,46; -0,28</t>
+          <t>-5,08; -0,05</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 1,07</t>
+          <t>-4,92; 0,96</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-62,9%</t>
+          <t>-62,5%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>-42,44%</t>
+          <t>-42,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1024,22 +1024,22 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 408,05</t>
+          <t>-100,0; 420,15</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 134,85</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 60,93</t>
+          <t>-100,0; 123,49</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-90,59; 133,53</t>
+          <t>-89,91; 104,3</t>
         </is>
       </c>
     </row>
@@ -1124,32 +1124,32 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 3,98</t>
+          <t>-1,43; 3,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 0,0</t>
+          <t>-3,58; 0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 7,38</t>
+          <t>-0,71; 7,1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 3,19</t>
+          <t>-0,67; 2,77</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 0,0</t>
+          <t>-1,99; 0,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 4,2</t>
+          <t>-0,43; 3,67</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>-3,07</t>
+          <t>-3,04</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-1,65</t>
+          <t>-1,64</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,58; -0,86</t>
+          <t>-7,65; -0,94</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,67; 0,38</t>
+          <t>-7,16; 0,09</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 39,92</t>
+          <t>-6,07; 34,68</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 1,73</t>
+          <t>-3,43; 1,85</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 2,32</t>
+          <t>-3,24; 2,55</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 0,13</t>
+          <t>-4,44; 0,11</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,71; -0,19</t>
+          <t>-4,71; -0,26</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 0,3</t>
+          <t>-4,05; 0,5</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 24,12</t>
+          <t>-3,96; 23,96</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>-58,34%</t>
+          <t>-57,86%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-41,78%</t>
+          <t>-41,45%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -8,01</t>
+          <t>-95,74; 16,41</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-86,88; 22,15</t>
+          <t>-85,76; 23,05</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 1758,18</t>
+          <t>-100,0; 1058,68</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-91,4; 167,82</t>
+          <t>-87,57; 207,94</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-79,53; 208,08</t>
+          <t>-82,1; 243,44</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 102,5</t>
+          <t>-100,0; 124,38</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-85,72; -1,37</t>
+          <t>-85,37; 3,88</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-74,81; 19,02</t>
+          <t>-73,85; 21,81</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-94,45; 732,46</t>
+          <t>-92,98; 983,73</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-12,03; -1,38</t>
+          <t>-12,64; -1,76</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-9,56; 1,52</t>
+          <t>-10,02; 1,53</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-10,82; 0,47</t>
+          <t>-10,74; 0,35</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-9,07; -1,59</t>
+          <t>-9,38; -1,62</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-7,68; 0,61</t>
+          <t>-8,24; 0,33</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-8,49; -0,42</t>
+          <t>-8,4; -0,4</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-8,56; -2,36</t>
+          <t>-8,52; -2,25</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-6,59; 0,03</t>
+          <t>-7,02; -0,01</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,8; -1,3</t>
+          <t>-7,28; -0,96</t>
         </is>
       </c>
     </row>
@@ -1647,17 +1647,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 31,98</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-90,97; 91,95</t>
+          <t>-88,99; 78,58</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-94,83; 46,09</t>
+          <t>-93,6; 57,55</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1667,27 +1667,27 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 113,91</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 43,28</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -47,62</t>
+          <t>-100,0; -47,64</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-83,98; 13,4</t>
+          <t>-84,71; 10,04</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-91,51; -25,86</t>
+          <t>-89,54; -11,04</t>
         </is>
       </c>
     </row>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0,9</t>
+          <t>0,95</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>-0,47</t>
+          <t>-0,45</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 6,59</t>
+          <t>-3,64; 6,98</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 5,04</t>
+          <t>-3,71; 4,97</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-7,35; -0,88</t>
+          <t>-6,66; -0,88</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-7,96; 3,42</t>
+          <t>-7,98; 3,31</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-10,78; -1,77</t>
+          <t>-11,74; -2,59</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-9,21; 0,41</t>
+          <t>-9,64; -0,16</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 3,49</t>
+          <t>-3,9; 3,4</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-6,18; 0,17</t>
+          <t>-6,11; 0,12</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-6,39; -0,6</t>
+          <t>-6,19; -0,72</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>34,05%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>-11,69%</t>
+          <t>-11,18%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-87,62; 177,8</t>
+          <t>-89,5; 165,03</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -1888,22 +1888,22 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 167,27</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-70,27; 151,1</t>
+          <t>-68,28; 170,07</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-93,58; 35,53</t>
+          <t>-92,97; 45,92</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 19,53</t>
+          <t>-100,0; -11,88</t>
         </is>
       </c>
     </row>
@@ -1925,7 +1925,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>-2,05</t>
+          <t>-2,04</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>-1,46</t>
+          <t>-1,45</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>-1,64</t>
+          <t>-1,63</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-0,54</t>
+          <t>-0,53</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,54; -0,02</t>
+          <t>-3,65; -0,17</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-3,82; -0,57</t>
+          <t>-3,92; -0,55</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 14,38</t>
+          <t>-3,64; 16,85</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,01; -0,11</t>
+          <t>-2,88; 0,07</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,36; -0,73</t>
+          <t>-3,33; -0,65</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-3,14; -0,36</t>
+          <t>-3,02; -0,25</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,77; -0,52</t>
+          <t>-2,81; -0,53</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-3,02; -0,96</t>
+          <t>-3,18; -0,91</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 5,97</t>
+          <t>-2,78; 5,99</t>
         </is>
       </c>
     </row>
@@ -2026,47 +2026,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>-47,31%</t>
+          <t>-47,18%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>-53,44%</t>
+          <t>-53,22%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>-48,41%</t>
+          <t>-48,27%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>-63,32%</t>
+          <t>-63,28%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-56,83%</t>
+          <t>-56,74%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>-48,04%</t>
+          <t>-47,9%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>-58,08%</t>
+          <t>-57,96%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-15,72%</t>
+          <t>-15,57%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-74,89; -0,63</t>
+          <t>-73,95; -3,48</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-76,27; -14,75</t>
+          <t>-75,87; -11,67</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-89,2; 518,93</t>
+          <t>-88,17; 520,97</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-77,18; -3,36</t>
+          <t>-75,65; 8,31</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-83,7; -24,95</t>
+          <t>-84,28; -23,79</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-77,82; -3,35</t>
+          <t>-76,79; -7,14</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-68,43; -18,54</t>
+          <t>-67,12; -16,02</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-73,88; -31,83</t>
+          <t>-75,83; -29,89</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-75,42; 190,38</t>
+          <t>-76,71; 185,92</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P5B_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P5B_R-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 6,79</t>
+          <t>-4,08; 6,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,73; -0,98</t>
+          <t>-8,09; -0,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,1; -0,98</t>
+          <t>-8,86; -0,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 2,85</t>
+          <t>-4,44; 3,44</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,02; 0,0</t>
+          <t>-6,3; 0,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 1,57</t>
+          <t>-4,31; 1,69</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 3,57</t>
+          <t>-2,88; 3,23</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,96; -1,24</t>
+          <t>-5,12; -0,93</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-5,17; -0,12</t>
+          <t>-4,92; -0,11</t>
         </is>
       </c>
     </row>
@@ -783,7 +783,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 627,99</t>
+          <t>-100,0; 470,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-72,94; 322,6</t>
+          <t>-72,29; 312,65</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 106,96</t>
+          <t>-100,0; 65,17</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 5,03</t>
+          <t>-5,11; 4,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,26; 0,42</t>
+          <t>-7,18; 0,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,07; 0,34</t>
+          <t>-7,18; 0,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,2; 1,66</t>
+          <t>-6,59; 2,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,81; 0,0</t>
+          <t>-7,0; 0,68</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 3,63</t>
+          <t>-5,28; 3,64</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,38; 1,81</t>
+          <t>-4,63; 1,8</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,08; -0,05</t>
+          <t>-5,57; -0,22</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 0,96</t>
+          <t>-4,62; 1,01</t>
         </is>
       </c>
     </row>
@@ -1024,22 +1024,22 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 420,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 134,85</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 123,49</t>
+          <t>-100,0; 34,01</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-89,91; 104,3</t>
+          <t>-89,94; 104,07</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,13</t>
+          <t>0,0; 6,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 3,35</t>
+          <t>-1,43; 3,3</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1134,22 +1134,22 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 7,1</t>
+          <t>-0,71; 7,03</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 2,77</t>
+          <t>-0,45; 3,17</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 0,0</t>
+          <t>-2,41; 0,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 3,67</t>
+          <t>-0,43; 3,89</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,65; -0,94</t>
+          <t>-7,8; -0,76</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,16; 0,09</t>
+          <t>-7,09; 0,23</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,07; 34,68</t>
+          <t>-6,32; 36,17</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 1,85</t>
+          <t>-3,58; 1,82</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 2,55</t>
+          <t>-2,87; 2,62</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 0,11</t>
+          <t>-4,85; 0,04</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,71; -0,26</t>
+          <t>-4,55; -0,26</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 0,5</t>
+          <t>-4,15; 0,52</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 23,96</t>
+          <t>-4,15; 20,89</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-95,74; 16,41</t>
+          <t>-93,86; 16,61</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-85,76; 23,05</t>
+          <t>-87,11; 19,93</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 1058,68</t>
+          <t>-100,0; 966,77</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-87,57; 207,94</t>
+          <t>-89,29; 195,6</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-82,1; 243,44</t>
+          <t>-75,43; 228,74</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 124,38</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-85,37; 3,88</t>
+          <t>-84,51; 2,91</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-73,85; 21,81</t>
+          <t>-73,93; 32,42</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-92,98; 983,73</t>
+          <t>-93,62; 736,4</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-12,64; -1,76</t>
+          <t>-11,61; -1,46</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-10,02; 1,53</t>
+          <t>-10,0; 1,99</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-10,74; 0,35</t>
+          <t>-10,31; 0,91</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-9,38; -1,62</t>
+          <t>-8,87; -1,58</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-8,24; 0,33</t>
+          <t>-7,66; 0,28</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-8,4; -0,4</t>
+          <t>-8,27; -0,56</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-8,52; -2,25</t>
+          <t>-8,84; -2,38</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-7,02; -0,01</t>
+          <t>-7,17; 0,18</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,28; -0,96</t>
+          <t>-7,74; -0,8</t>
         </is>
       </c>
     </row>
@@ -1647,17 +1647,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 31,98</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-88,99; 78,58</t>
+          <t>-88,94; 105,44</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-93,6; 57,55</t>
+          <t>-93,27; 65,06</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1667,27 +1667,27 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 113,91</t>
+          <t>-100,0; 107,93</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 11,79</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -47,64</t>
+          <t>-100,0; -48,56</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-84,71; 10,04</t>
+          <t>-84,15; 20,68</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-89,54; -11,04</t>
+          <t>-90,95; -12,98</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 6,98</t>
+          <t>-3,54; 6,75</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 4,97</t>
+          <t>-4,33; 5,26</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-6,66; -0,88</t>
+          <t>-7,4; -0,88</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-7,98; 3,31</t>
+          <t>-7,12; 3,34</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-11,74; -2,59</t>
+          <t>-10,76; -1,9</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-9,64; -0,16</t>
+          <t>-9,22; 0,43</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 3,4</t>
+          <t>-4,03; 2,89</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 0,12</t>
+          <t>-5,9; 0,08</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-6,19; -0,72</t>
+          <t>-6,85; -0,92</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-89,5; 165,03</t>
+          <t>-86,59; 192,74</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -1888,22 +1888,22 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 79,0</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-68,28; 170,07</t>
+          <t>-74,68; 130,27</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-92,97; 45,92</t>
+          <t>-92,94; 31,01</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -11,88</t>
+          <t>-100,0; -10,21</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,65; -0,17</t>
+          <t>-3,47; -0,13</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-3,92; -0,55</t>
+          <t>-3,78; -0,51</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 16,85</t>
+          <t>-3,72; 15,04</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 0,07</t>
+          <t>-2,82; -0,01</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,33; -0,65</t>
+          <t>-3,27; -0,56</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-3,02; -0,25</t>
+          <t>-3,06; -0,36</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,81; -0,53</t>
+          <t>-2,72; -0,49</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-3,18; -0,91</t>
+          <t>-3,04; -0,93</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 5,99</t>
+          <t>-2,72; 7,78</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-73,95; -3,48</t>
+          <t>-74,21; -0,42</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-75,87; -11,67</t>
+          <t>-75,5; -16,17</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-88,17; 520,97</t>
+          <t>-89,54; 553,98</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-75,65; 8,31</t>
+          <t>-75,26; 1,99</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-84,28; -23,79</t>
+          <t>-84,65; -21,76</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-76,79; -7,14</t>
+          <t>-78,83; -13,15</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-67,12; -16,02</t>
+          <t>-67,55; -17,25</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-75,83; -29,89</t>
+          <t>-75,12; -33,57</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-76,71; 185,92</t>
+          <t>-75,46; 293,12</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P5B_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P5B_R-Clase-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,34 +624,34 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-0,03</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-1,81</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-0,63</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>0,89</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-3,5</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>-3,5</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-0,03</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-1,81</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-0,72</t>
-        </is>
-      </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
           <t>0,26</t>
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-2,08</t>
+          <t>-2,07</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 6,76</t>
+          <t>-3,79; 3,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,09; -0,98</t>
+          <t>-6,83; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,86; -0,98</t>
+          <t>-4,2; 1,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 3,44</t>
+          <t>-3,78; 6,7</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,3; 0,0</t>
+          <t>-7,96; -0,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 1,69</t>
+          <t>-7,96; -0,97</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 3,23</t>
+          <t>-2,77; 3,42</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,12; -0,93</t>
+          <t>-5,6; -0,97</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,92; -0,11</t>
+          <t>-4,95; -0,09</t>
         </is>
       </c>
     </row>
@@ -730,47 +730,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-1,69%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-34,96%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>25,44%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-1,69%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>9,77%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-39,42%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>9,77%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-77,0%</t>
+          <t>-76,34%</t>
         </is>
       </c>
     </row>
@@ -783,7 +783,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 470,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-83,52; 484,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-72,29; 312,65</t>
+          <t>-72,58; 293,25</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 65,17</t>
+          <t>-100,0; 122,31</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-2,21</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-2,72</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-0,85</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-0,51</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-2,23</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-2,27</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-2,21</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-2,72</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,92</t>
+          <t>-2,19</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-1,59</t>
+          <t>-1,54</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 4,21</t>
+          <t>-6,6; 1,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,18; 0,73</t>
+          <t>-8,1; 0,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,18; 0,48</t>
+          <t>-5,75; 3,62</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,59; 2,1</t>
+          <t>-4,66; 4,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,0; 0,68</t>
+          <t>-7,26; 0,51</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 3,64</t>
+          <t>-7,14; 0,48</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 1,8</t>
+          <t>-4,75; 1,78</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,57; -0,22</t>
+          <t>-5,46; -0,28</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 1,01</t>
+          <t>-4,88; 1,24</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-62,5%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-76,82%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-24,07%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-17,29%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-74,95%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-76,31%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-62,5%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-76,82%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-26,02%</t>
+          <t>-73,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-48,81%</t>
+          <t>-47,42%</t>
         </is>
       </c>
     </row>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 424,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1034,12 +1034,12 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 34,01</t>
+          <t>-100,0; 60,93</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-89,94; 104,07</t>
+          <t>-90,08; 143,36</t>
         </is>
       </c>
     </row>
@@ -1056,34 +1056,34 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,29</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-0,71</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1,8</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>1,15</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,29</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-0,71</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,52</t>
-        </is>
-      </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
           <t>0,66</t>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,81</t>
+          <t>0,87</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,77</t>
+          <t>-1,43; 3,98</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,6; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,71; 8,46</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 3,3</t>
+          <t>0,0; 6,13</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 7,03</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 3,17</t>
+          <t>-0,69; 3,19</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 0,0</t>
+          <t>-2,12; 0,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 3,89</t>
+          <t>-0,42; 4,59</t>
         </is>
       </c>
     </row>
@@ -1162,47 +1162,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>40,58%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>252,38%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>40,58%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>156,15%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>213,31%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>156,15%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>192,85%</t>
+          <t>207,79%</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-0,85</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,22</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-1,91</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-3,86</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-3,04</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>7,26</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,85</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-0,22</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-1,91</t>
+          <t>-3,44</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2,67</t>
+          <t>-2,72</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,8; -0,76</t>
+          <t>-3,87; 1,73</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,09; 0,23</t>
+          <t>-3,15; 2,32</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 36,17</t>
+          <t>-4,54; 0,2</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 1,82</t>
+          <t>-7,58; -0,86</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 2,62</t>
+          <t>-6,53; 0,42</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 0,04</t>
+          <t>-6,78; 2,74</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,55; -0,26</t>
+          <t>-4,71; -0,19</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 0,52</t>
+          <t>-3,97; 0,55</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 20,89</t>
+          <t>-5,17; -0,11</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-32,33%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-8,35%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-72,37%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-73,32%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-57,86%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>138,08%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-32,33%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-8,35%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-72,55%</t>
+          <t>-65,5%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>67,42%</t>
+          <t>-68,69%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-93,86; 16,61</t>
+          <t>-91,4; 167,82</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-87,11; 19,93</t>
+          <t>-79,53; 208,08</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 966,77</t>
+          <t>-100,0; 117,73</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-89,29; 195,6</t>
+          <t>-100,0; -8,01</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-75,43; 228,74</t>
+          <t>-87,39; 26,26</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 221,56</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-84,51; 2,91</t>
+          <t>-85,72; -1,37</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-73,93; 32,42</t>
+          <t>-73,17; 30,95</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-93,62; 736,4</t>
+          <t>-95,19; 41,28</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-4,54</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-3,12</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-3,48</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-5,59</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-3,07</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-4,09</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-4,54</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-3,12</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-3,52</t>
+          <t>-4,02</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-3,81</t>
+          <t>-3,73</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-11,61; -1,46</t>
+          <t>-9,07; -1,59</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-10,0; 1,99</t>
+          <t>-7,68; 0,61</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-10,31; 0,91</t>
+          <t>-8,44; -0,29</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-8,87; -1,58</t>
+          <t>-12,03; -1,38</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-7,66; 0,28</t>
+          <t>-9,56; 1,52</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-8,27; -0,56</t>
+          <t>-10,77; 0,61</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-8,84; -2,38</t>
+          <t>-8,56; -2,36</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 0,18</t>
+          <t>-6,59; 0,03</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,74; -0,8</t>
+          <t>-7,77; -1,15</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-68,75%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-76,7%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-88,25%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-48,51%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-64,59%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-68,75%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-77,63%</t>
+          <t>-63,46%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-71,29%</t>
+          <t>-69,77%</t>
         </is>
       </c>
     </row>
@@ -1647,17 +1647,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-88,94; 105,44</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-93,27; 65,06</t>
+          <t>-100,0; 49,48</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1667,27 +1667,27 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 107,93</t>
+          <t>-90,97; 91,95</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 11,79</t>
+          <t>-94,35; 52,88</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -48,56</t>
+          <t>-100,0; -47,62</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-84,15; 20,68</t>
+          <t>-83,98; 13,4</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-90,95; -12,98</t>
+          <t>-91,58; -23,22</t>
         </is>
       </c>
     </row>
@@ -1704,34 +1704,34 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>-1,86</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-5,36</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>-4,03</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>0,95</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>0,2</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>-2,78</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>-1,86</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>-5,36</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>-3,84</t>
-        </is>
-      </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
           <t>-0,45</t>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-3,27</t>
+          <t>-3,4</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 6,75</t>
+          <t>-7,96; 3,42</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 5,26</t>
+          <t>-10,78; -1,77</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-7,4; -0,88</t>
+          <t>-9,47; 0,04</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-7,12; 3,34</t>
+          <t>-3,48; 7,42</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-10,76; -1,9</t>
+          <t>-3,83; 5,04</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-9,22; 0,43</t>
+          <t>-7,35; -0,88</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 2,89</t>
+          <t>-3,97; 3,24</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 0,08</t>
+          <t>-6,18; 0,17</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-6,85; -0,92</t>
+          <t>-6,49; -0,81</t>
         </is>
       </c>
     </row>
@@ -1810,34 +1810,34 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>-34,68%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>-75,14%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>34,05%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>7,14%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>-34,68%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>-71,55%</t>
-        </is>
-      </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
           <t>-11,18%</t>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-80,76%</t>
+          <t>-83,8%</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-87,62; 177,8</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 130,11</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-86,59; 192,74</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -1888,22 +1888,22 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 79,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-74,68; 130,27</t>
+          <t>-69,75; 161,39</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-92,94; 31,01</t>
+          <t>-93,58; 35,53</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -10,21</t>
+          <t>-100,0; 3,25</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-1,45</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-1,91</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>-1,67</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>-1,81</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>-2,04</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>0,84</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-1,45</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>-1,91</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-1,71</t>
+          <t>-2,74</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-0,53</t>
+          <t>-2,19</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,47; -0,13</t>
+          <t>-2,89; 0,01</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-3,78; -0,51</t>
+          <t>-3,38; -0,63</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 15,04</t>
+          <t>-3,03; -0,29</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,82; -0,01</t>
+          <t>-3,54; -0,1</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,27; -0,56</t>
+          <t>-3,84; -0,49</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-3,06; -0,36</t>
+          <t>-4,28; -0,68</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,72; -0,49</t>
+          <t>-2,67; -0,45</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-3,04; -0,93</t>
+          <t>-3,12; -0,96</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 7,78</t>
+          <t>-3,18; -1,04</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-48,27%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-63,28%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>-55,29%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>-47,18%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>-53,22%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>21,95%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-48,27%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>-63,28%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-56,74%</t>
+          <t>-71,58%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-15,57%</t>
+          <t>-64,12%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-74,21; -0,42</t>
+          <t>-76,06; 6,26</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-75,5; -16,17</t>
+          <t>-84,65; -20,03</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-89,54; 553,98</t>
+          <t>-78,04; -12,96</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-75,26; 1,99</t>
+          <t>-72,53; 2,67</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-84,65; -21,76</t>
+          <t>-76,5; -12,63</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-78,83; -13,15</t>
+          <t>-90,42; -8,83</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-67,55; -17,25</t>
+          <t>-67,41; -14,85</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-75,12; -33,57</t>
+          <t>-74,6; -32,74</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-75,46; 293,12</t>
+          <t>-78,4; -33,58</t>
         </is>
       </c>
     </row>
